--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_314_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_314_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,10 +1335,10 @@
         <v>21</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
         <v>2</v>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2511,10 +2511,10 @@
         <v>17</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
@@ -3827,16 +3827,16 @@
         <v>93</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X30" t="n">
         <v>24</v>
@@ -4491,13 +4491,13 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X36" t="n">
         <v>2</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         <v>21</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>2</v>
@@ -5468,7 +5468,7 @@
         <v>18</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -5860,16 +5860,16 @@
         <v>22</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X43" t="n">
         <v>5</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
         <v>1</v>
@@ -6588,16 +6588,16 @@
         <v>124</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X47" t="n">
         <v>23</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_314_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_314_EL.xlsx
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
         <v>8</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>82.76</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
         <v>17</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>74.19</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2131,14 +2131,14 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA21" t="n">
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3307,14 +3307,14 @@
         <v>2</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="Y30" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4500,14 +4500,14 @@
         <v>3</v>
       </c>
       <c r="X36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="n">
         <v>3</v>
       </c>
-      <c r="Y38" t="n">
-        <v>5</v>
-      </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5088,14 +5088,14 @@
         <v>2</v>
       </c>
       <c r="X39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5480,10 +5480,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -5872,10 +5872,10 @@
         <v>2</v>
       </c>
       <c r="X43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -6600,14 +6600,14 @@
         <v>8</v>
       </c>
       <c r="X47" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="Y47" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA47" t="n">
